--- a/output/roomself_excel/11101.xlsx
+++ b/output/roomself_excel/11101.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>190578</v>
+        <v>25284</v>
       </c>
       <c r="D2" t="n">
-        <v>4020</v>
+        <v>1300</v>
       </c>
       <c r="E2" t="n">
-        <v>708</v>
+        <v>224</v>
       </c>
       <c r="F2" t="n">
-        <v>506</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25284</v>
+        <v>12312</v>
       </c>
       <c r="D3" t="n">
-        <v>1300</v>
+        <v>888</v>
       </c>
       <c r="E3" t="n">
-        <v>224</v>
+        <v>136</v>
       </c>
       <c r="F3" t="n">
-        <v>146</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20634</v>
+        <v>190578</v>
       </c>
       <c r="D4" t="n">
-        <v>1180</v>
+        <v>4020</v>
       </c>
       <c r="E4" t="n">
-        <v>181</v>
+        <v>708</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34041</v>
+        <v>20634</v>
       </c>
       <c r="D5" t="n">
-        <v>1576</v>
+        <v>1180</v>
       </c>
       <c r="E5" t="n">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="F5" t="n">
-        <v>146</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12312</v>
+        <v>34041</v>
       </c>
       <c r="D6" t="n">
-        <v>888</v>
+        <v>1576</v>
       </c>
       <c r="E6" t="n">
-        <v>136</v>
+        <v>281</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11101.xlsx
+++ b/output/roomself_excel/11101.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>1300</v>
       </c>
-      <c r="E2" t="n">
-        <v>224</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>146</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>196</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,31 @@
       <c r="D3" t="n">
         <v>888</v>
       </c>
-      <c r="E3" t="n">
-        <v>136</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>114</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +592,38 @@
       <c r="D4" t="n">
         <v>4020</v>
       </c>
-      <c r="E4" t="n">
-        <v>708</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>343</v>
+        <v>323</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>620</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>187</v>
+      </c>
+      <c r="M4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +641,23 @@
       <c r="D5" t="n">
         <v>1180</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>181</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>32</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,11 +674,38 @@
       <c r="D6" t="n">
         <v>1576</v>
       </c>
-      <c r="E6" t="n">
-        <v>281</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>146</v>
+        <v>261</v>
+      </c>
+      <c r="G6" t="n">
+        <v>17</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>36</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>93</v>
+      </c>
+      <c r="M6" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/11101.xlsx
+++ b/output/roomself_excel/11101.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,26 @@
           <t>ExtWallWidth_3</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -535,6 +555,22 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -576,6 +612,10 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -624,6 +664,22 @@
       </c>
       <c r="M4" t="n">
         <v>18</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -658,6 +714,10 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -705,6 +765,22 @@
         <v>93</v>
       </c>
       <c r="M6" t="n">
+        <v>16</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q6" t="n">
         <v>16</v>
       </c>
     </row>
